--- a/verification/cases/roundtrip/data_validation/init.xlsx
+++ b/verification/cases/roundtrip/data_validation/init.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="16925"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GregWoolsey\git\poi\test-data\spreadsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E07FF88-B408-406D-95CA-89D8DF41C506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,22 +18,33 @@
   <definedNames>
     <definedName name="ValueTable">Table1[List Values]</definedName>
   </definedNames>
-  <calcPr calcId="171027" calcMode="manual"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Greg Woolsey</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -230,7 +242,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -326,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -338,7 +350,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,10 +368,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="F1:F13" totalsRowShown="0">
-  <autoFilter ref="F1:F13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="F1:F13" totalsRowShown="0">
+  <autoFilter ref="F1:F13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="List Values"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="List Values"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -662,20 +673,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -696,7 +707,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -717,7 +728,7 @@
         <v>58806</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -735,7 +746,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -753,7 +764,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -773,7 +784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -793,7 +804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -814,7 +825,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -834,7 +845,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -850,11 +861,11 @@
       <c r="H9" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -870,11 +881,11 @@
       <c r="H10" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -890,11 +901,11 @@
       <c r="H11" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -908,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -922,7 +933,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -933,7 +944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -944,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -955,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -966,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -977,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -988,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -999,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1010,7 +1021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1021,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1032,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1046,7 +1057,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1057,7 +1068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1068,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1079,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1090,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1101,7 +1112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1112,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -1123,7 +1134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1134,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -1145,7 +1156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -1156,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -1169,60 +1180,60 @@
     </row>
   </sheetData>
   <dataValidations count="17">
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" showInputMessage="1" showErrorMessage="1" sqref="B4">
+    <dataValidation type="textLength" operator="greaterThan" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B7">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B7" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:B9">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:B9" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>E1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:B16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:B16" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>ValueTable</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>D2</formula1>
       <formula2>F2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B32">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B32" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>F2</formula1>
       <formula2>D2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B29">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B29" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>F1</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>36161</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18:B19">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18:B19" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>I1</formula1>
       <formula2>I2</formula2>
     </dataValidation>
-    <dataValidation type="time" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
+    <dataValidation type="time" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>0.333333333333333</formula1>
     </dataValidation>
-    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21">
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>I3</formula1>
       <formula2>I4</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B23">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B23" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>25</formula1>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B28">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B28" xr:uid="{00000000-0002-0000-0000-00000F000000}">
       <formula1>I5</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:B35">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:B35" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>I9</formula1>
     </dataValidation>
   </dataValidations>
